--- a/africanborderlandshandbook.xlsx
+++ b/africanborderlandshandbook.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owalther\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owalther\UF Dropbox\Olivier Walther\RoutledgeHandbook\stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{960F2C7D-5CE8-439A-8E5D-6D4BA2ED3597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE121066-99A7-4294-BBEB-FC194AA6741F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{340F51F2-2262-4219-B6EF-B689B87D0E7A}"/>
   </bookViews>
   <sheets>
-    <sheet name="data" sheetId="1" r:id="rId1"/>
+    <sheet name="network" sheetId="1" r:id="rId1"/>
+    <sheet name="citations" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="1144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="1146">
   <si>
     <t>reference</t>
   </si>
@@ -3471,6 +3472,12 @@
   </si>
   <si>
     <t>Zoubir, Y. (2024, November 4). Ethiopia and Somalia on the edge of war. Middle East Council on Global Affairs.</t>
+  </si>
+  <si>
+    <t>rank</t>
+  </si>
+  <si>
+    <t>nb of times cited</t>
   </si>
 </sst>
 </file>
@@ -3523,9 +3530,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18215,4 +18225,9129 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55D9D7F3-9E61-46B0-A308-6FC3822E0B50}">
+  <dimension ref="A1:C1100"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>387</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>839</v>
+      </c>
+      <c r="C3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>820</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>831</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1183</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2">
+        <v>729</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2">
+        <v>867</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9" s="2">
+        <v>892</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10" s="2">
+        <v>313</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11" s="2">
+        <v>623</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2">
+        <v>873</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>5</v>
+      </c>
+      <c r="B13" s="2">
+        <v>936</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1048</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1211</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>6</v>
+      </c>
+      <c r="B16" s="2">
+        <v>69</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>6</v>
+      </c>
+      <c r="B17" s="2">
+        <v>884</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>6</v>
+      </c>
+      <c r="B18" s="2">
+        <v>900</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>6</v>
+      </c>
+      <c r="B19" s="2">
+        <v>964</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>6</v>
+      </c>
+      <c r="B20" s="2">
+        <v>1018</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>6</v>
+      </c>
+      <c r="B21" s="2">
+        <v>1176</v>
+      </c>
+      <c r="C21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>6</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1202</v>
+      </c>
+      <c r="C22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>7</v>
+      </c>
+      <c r="B23" s="2">
+        <v>80</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>7</v>
+      </c>
+      <c r="B24" s="2">
+        <v>83</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>7</v>
+      </c>
+      <c r="B25" s="2">
+        <v>307</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>7</v>
+      </c>
+      <c r="B26" s="2">
+        <v>328</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>7</v>
+      </c>
+      <c r="B27" s="2">
+        <v>412</v>
+      </c>
+      <c r="C27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>7</v>
+      </c>
+      <c r="B28" s="2">
+        <v>427</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>7</v>
+      </c>
+      <c r="B29" s="2">
+        <v>487</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>7</v>
+      </c>
+      <c r="B30" s="2">
+        <v>511</v>
+      </c>
+      <c r="C30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>7</v>
+      </c>
+      <c r="B31" s="2">
+        <v>513</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>7</v>
+      </c>
+      <c r="B32" s="2">
+        <v>527</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>7</v>
+      </c>
+      <c r="B33" s="2">
+        <v>576</v>
+      </c>
+      <c r="C33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>7</v>
+      </c>
+      <c r="B34" s="2">
+        <v>599</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>7</v>
+      </c>
+      <c r="B35" s="2">
+        <v>602</v>
+      </c>
+      <c r="C35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>7</v>
+      </c>
+      <c r="B36" s="2">
+        <v>618</v>
+      </c>
+      <c r="C36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>7</v>
+      </c>
+      <c r="B37" s="2">
+        <v>664</v>
+      </c>
+      <c r="C37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>7</v>
+      </c>
+      <c r="B38" s="2">
+        <v>735</v>
+      </c>
+      <c r="C38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>7</v>
+      </c>
+      <c r="B39" s="2">
+        <v>749</v>
+      </c>
+      <c r="C39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>7</v>
+      </c>
+      <c r="B40" s="2">
+        <v>755</v>
+      </c>
+      <c r="C40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>7</v>
+      </c>
+      <c r="B41" s="2">
+        <v>849</v>
+      </c>
+      <c r="C41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>7</v>
+      </c>
+      <c r="B42" s="2">
+        <v>877</v>
+      </c>
+      <c r="C42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>7</v>
+      </c>
+      <c r="B43" s="2">
+        <v>882</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>7</v>
+      </c>
+      <c r="B44" s="2">
+        <v>1098</v>
+      </c>
+      <c r="C44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>7</v>
+      </c>
+      <c r="B45" s="2">
+        <v>1119</v>
+      </c>
+      <c r="C45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>7</v>
+      </c>
+      <c r="B46" s="2">
+        <v>1194</v>
+      </c>
+      <c r="C46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>7</v>
+      </c>
+      <c r="B47" s="2">
+        <v>1197</v>
+      </c>
+      <c r="C47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>8</v>
+      </c>
+      <c r="B48" s="2">
+        <v>21</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>8</v>
+      </c>
+      <c r="B49" s="2">
+        <v>28</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>8</v>
+      </c>
+      <c r="B50" s="2">
+        <v>43</v>
+      </c>
+      <c r="C50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>8</v>
+      </c>
+      <c r="B51" s="2">
+        <v>51</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>8</v>
+      </c>
+      <c r="B52" s="2">
+        <v>75</v>
+      </c>
+      <c r="C52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>8</v>
+      </c>
+      <c r="B53" s="2">
+        <v>108</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>8</v>
+      </c>
+      <c r="B54" s="2">
+        <v>128</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>8</v>
+      </c>
+      <c r="B55" s="2">
+        <v>160</v>
+      </c>
+      <c r="C55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>8</v>
+      </c>
+      <c r="B56" s="2">
+        <v>172</v>
+      </c>
+      <c r="C56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>8</v>
+      </c>
+      <c r="B57" s="2">
+        <v>188</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>8</v>
+      </c>
+      <c r="B58" s="2">
+        <v>199</v>
+      </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>8</v>
+      </c>
+      <c r="B59" s="2">
+        <v>235</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>8</v>
+      </c>
+      <c r="B60" s="2">
+        <v>258</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>8</v>
+      </c>
+      <c r="B61" s="2">
+        <v>298</v>
+      </c>
+      <c r="C61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>8</v>
+      </c>
+      <c r="B62" s="2">
+        <v>319</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>8</v>
+      </c>
+      <c r="B63" s="2">
+        <v>321</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>8</v>
+      </c>
+      <c r="B64" s="2">
+        <v>375</v>
+      </c>
+      <c r="C64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>8</v>
+      </c>
+      <c r="B65" s="2">
+        <v>377</v>
+      </c>
+      <c r="C65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>8</v>
+      </c>
+      <c r="B66" s="2">
+        <v>383</v>
+      </c>
+      <c r="C66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>8</v>
+      </c>
+      <c r="B67" s="2">
+        <v>403</v>
+      </c>
+      <c r="C67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>8</v>
+      </c>
+      <c r="B68" s="2">
+        <v>405</v>
+      </c>
+      <c r="C68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>8</v>
+      </c>
+      <c r="B69" s="2">
+        <v>406</v>
+      </c>
+      <c r="C69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>8</v>
+      </c>
+      <c r="B70" s="2">
+        <v>419</v>
+      </c>
+      <c r="C70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>8</v>
+      </c>
+      <c r="B71" s="2">
+        <v>424</v>
+      </c>
+      <c r="C71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>8</v>
+      </c>
+      <c r="B72" s="2">
+        <v>448</v>
+      </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>8</v>
+      </c>
+      <c r="B73" s="2">
+        <v>450</v>
+      </c>
+      <c r="C73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>8</v>
+      </c>
+      <c r="B74" s="2">
+        <v>483</v>
+      </c>
+      <c r="C74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>8</v>
+      </c>
+      <c r="B75" s="2">
+        <v>500</v>
+      </c>
+      <c r="C75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>8</v>
+      </c>
+      <c r="B76" s="2">
+        <v>504</v>
+      </c>
+      <c r="C76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>8</v>
+      </c>
+      <c r="B77" s="2">
+        <v>541</v>
+      </c>
+      <c r="C77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>8</v>
+      </c>
+      <c r="B78" s="2">
+        <v>637</v>
+      </c>
+      <c r="C78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>8</v>
+      </c>
+      <c r="B79" s="2">
+        <v>692</v>
+      </c>
+      <c r="C79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>8</v>
+      </c>
+      <c r="B80" s="2">
+        <v>711</v>
+      </c>
+      <c r="C80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>8</v>
+      </c>
+      <c r="B81" s="2">
+        <v>714</v>
+      </c>
+      <c r="C81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>8</v>
+      </c>
+      <c r="B82" s="2">
+        <v>716</v>
+      </c>
+      <c r="C82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>8</v>
+      </c>
+      <c r="B83" s="2">
+        <v>752</v>
+      </c>
+      <c r="C83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>8</v>
+      </c>
+      <c r="B84" s="2">
+        <v>764</v>
+      </c>
+      <c r="C84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>8</v>
+      </c>
+      <c r="B85" s="2">
+        <v>777</v>
+      </c>
+      <c r="C85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>8</v>
+      </c>
+      <c r="B86" s="2">
+        <v>814</v>
+      </c>
+      <c r="C86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>8</v>
+      </c>
+      <c r="B87" s="2">
+        <v>837</v>
+      </c>
+      <c r="C87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>8</v>
+      </c>
+      <c r="B88" s="2">
+        <v>880</v>
+      </c>
+      <c r="C88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>8</v>
+      </c>
+      <c r="B89" s="2">
+        <v>972</v>
+      </c>
+      <c r="C89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>8</v>
+      </c>
+      <c r="B90" s="2">
+        <v>1008</v>
+      </c>
+      <c r="C90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>8</v>
+      </c>
+      <c r="B91" s="2">
+        <v>1073</v>
+      </c>
+      <c r="C91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>8</v>
+      </c>
+      <c r="B92" s="2">
+        <v>1118</v>
+      </c>
+      <c r="C92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>8</v>
+      </c>
+      <c r="B93" s="2">
+        <v>1123</v>
+      </c>
+      <c r="C93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>8</v>
+      </c>
+      <c r="B94" s="2">
+        <v>1144</v>
+      </c>
+      <c r="C94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>8</v>
+      </c>
+      <c r="B95" s="2">
+        <v>1170</v>
+      </c>
+      <c r="C95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>8</v>
+      </c>
+      <c r="B96" s="2">
+        <v>1172</v>
+      </c>
+      <c r="C96">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>8</v>
+      </c>
+      <c r="B97" s="2">
+        <v>1174</v>
+      </c>
+      <c r="C97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>8</v>
+      </c>
+      <c r="B98" s="2">
+        <v>1181</v>
+      </c>
+      <c r="C98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>8</v>
+      </c>
+      <c r="B99" s="2">
+        <v>1190</v>
+      </c>
+      <c r="C99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>8</v>
+      </c>
+      <c r="B100" s="2">
+        <v>1192</v>
+      </c>
+      <c r="C100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>8</v>
+      </c>
+      <c r="B101" s="2">
+        <v>1200</v>
+      </c>
+      <c r="C101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>8</v>
+      </c>
+      <c r="B102" s="2">
+        <v>1206</v>
+      </c>
+      <c r="C102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>8</v>
+      </c>
+      <c r="B103" s="2">
+        <v>1209</v>
+      </c>
+      <c r="C103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>8</v>
+      </c>
+      <c r="B104" s="2">
+        <v>1235</v>
+      </c>
+      <c r="C104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>8</v>
+      </c>
+      <c r="B105" s="2">
+        <v>1293</v>
+      </c>
+      <c r="C105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B106" s="2">
+        <v>1</v>
+      </c>
+      <c r="C106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B107" s="2">
+        <v>2</v>
+      </c>
+      <c r="C107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B108" s="2">
+        <v>3</v>
+      </c>
+      <c r="C108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B109" s="2">
+        <v>4</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B110" s="2">
+        <v>5</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B111" s="2">
+        <v>6</v>
+      </c>
+      <c r="C111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B112" s="2">
+        <v>7</v>
+      </c>
+      <c r="C112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B113" s="2">
+        <v>8</v>
+      </c>
+      <c r="C113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B114" s="2">
+        <v>9</v>
+      </c>
+      <c r="C114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B115" s="2">
+        <v>10</v>
+      </c>
+      <c r="C115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B116" s="2">
+        <v>11</v>
+      </c>
+      <c r="C116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B117" s="2">
+        <v>12</v>
+      </c>
+      <c r="C117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B118" s="2">
+        <v>13</v>
+      </c>
+      <c r="C118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B119" s="2">
+        <v>14</v>
+      </c>
+      <c r="C119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B120" s="2">
+        <v>15</v>
+      </c>
+      <c r="C120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B121" s="2">
+        <v>16</v>
+      </c>
+      <c r="C121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B122" s="2">
+        <v>17</v>
+      </c>
+      <c r="C122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B123" s="2">
+        <v>18</v>
+      </c>
+      <c r="C123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B124" s="2">
+        <v>19</v>
+      </c>
+      <c r="C124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B125" s="2">
+        <v>20</v>
+      </c>
+      <c r="C125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B126" s="2">
+        <v>23</v>
+      </c>
+      <c r="C126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B127" s="2">
+        <v>24</v>
+      </c>
+      <c r="C127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B128" s="2">
+        <v>25</v>
+      </c>
+      <c r="C128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B129" s="2">
+        <v>26</v>
+      </c>
+      <c r="C129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B130" s="2">
+        <v>27</v>
+      </c>
+      <c r="C130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B131" s="2">
+        <v>31</v>
+      </c>
+      <c r="C131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B132" s="2">
+        <v>32</v>
+      </c>
+      <c r="C132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B133" s="2">
+        <v>33</v>
+      </c>
+      <c r="C133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B134" s="2">
+        <v>34</v>
+      </c>
+      <c r="C134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B135" s="2">
+        <v>35</v>
+      </c>
+      <c r="C135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B136" s="2">
+        <v>36</v>
+      </c>
+      <c r="C136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B137" s="2">
+        <v>37</v>
+      </c>
+      <c r="C137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B138" s="2">
+        <v>38</v>
+      </c>
+      <c r="C138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B139" s="2">
+        <v>39</v>
+      </c>
+      <c r="C139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B140" s="2">
+        <v>40</v>
+      </c>
+      <c r="C140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B141" s="2">
+        <v>41</v>
+      </c>
+      <c r="C141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B142" s="2">
+        <v>42</v>
+      </c>
+      <c r="C142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B143" s="2">
+        <v>45</v>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B144" s="2">
+        <v>46</v>
+      </c>
+      <c r="C144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B145" s="2">
+        <v>47</v>
+      </c>
+      <c r="C145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B146" s="2">
+        <v>48</v>
+      </c>
+      <c r="C146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B147" s="2">
+        <v>49</v>
+      </c>
+      <c r="C147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B148" s="2">
+        <v>50</v>
+      </c>
+      <c r="C148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B149" s="2">
+        <v>53</v>
+      </c>
+      <c r="C149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B150" s="2">
+        <v>54</v>
+      </c>
+      <c r="C150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B151" s="2">
+        <v>55</v>
+      </c>
+      <c r="C151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B152" s="2">
+        <v>56</v>
+      </c>
+      <c r="C152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B153" s="2">
+        <v>57</v>
+      </c>
+      <c r="C153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B154" s="2">
+        <v>58</v>
+      </c>
+      <c r="C154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B155" s="2">
+        <v>59</v>
+      </c>
+      <c r="C155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B156" s="2">
+        <v>60</v>
+      </c>
+      <c r="C156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B157" s="2">
+        <v>61</v>
+      </c>
+      <c r="C157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B158" s="2">
+        <v>62</v>
+      </c>
+      <c r="C158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B159" s="2">
+        <v>63</v>
+      </c>
+      <c r="C159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B160" s="2">
+        <v>64</v>
+      </c>
+      <c r="C160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B161" s="2">
+        <v>65</v>
+      </c>
+      <c r="C161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B162" s="2">
+        <v>66</v>
+      </c>
+      <c r="C162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B163" s="2">
+        <v>67</v>
+      </c>
+      <c r="C163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B164" s="2">
+        <v>68</v>
+      </c>
+      <c r="C164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B165" s="2">
+        <v>73</v>
+      </c>
+      <c r="C165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B166" s="2">
+        <v>74</v>
+      </c>
+      <c r="C166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B167" s="2">
+        <v>77</v>
+      </c>
+      <c r="C167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B168" s="2">
+        <v>78</v>
+      </c>
+      <c r="C168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B169" s="2">
+        <v>79</v>
+      </c>
+      <c r="C169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B170" s="2">
+        <v>86</v>
+      </c>
+      <c r="C170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B171" s="2">
+        <v>87</v>
+      </c>
+      <c r="C171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B172" s="2">
+        <v>88</v>
+      </c>
+      <c r="C172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B173" s="2">
+        <v>89</v>
+      </c>
+      <c r="C173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B174" s="2">
+        <v>90</v>
+      </c>
+      <c r="C174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B175" s="2">
+        <v>91</v>
+      </c>
+      <c r="C175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B176" s="2">
+        <v>92</v>
+      </c>
+      <c r="C176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B177" s="2">
+        <v>93</v>
+      </c>
+      <c r="C177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B178" s="2">
+        <v>94</v>
+      </c>
+      <c r="C178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B179" s="2">
+        <v>95</v>
+      </c>
+      <c r="C179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B180" s="2">
+        <v>96</v>
+      </c>
+      <c r="C180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B181" s="2">
+        <v>97</v>
+      </c>
+      <c r="C181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B182" s="2">
+        <v>98</v>
+      </c>
+      <c r="C182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B183" s="2">
+        <v>99</v>
+      </c>
+      <c r="C183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B184" s="2">
+        <v>100</v>
+      </c>
+      <c r="C184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B185" s="2">
+        <v>101</v>
+      </c>
+      <c r="C185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B186" s="2">
+        <v>102</v>
+      </c>
+      <c r="C186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B187" s="2">
+        <v>103</v>
+      </c>
+      <c r="C187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B188" s="2">
+        <v>104</v>
+      </c>
+      <c r="C188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B189" s="2">
+        <v>105</v>
+      </c>
+      <c r="C189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B190" s="2">
+        <v>106</v>
+      </c>
+      <c r="C190">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B191" s="2">
+        <v>107</v>
+      </c>
+      <c r="C191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B192" s="2">
+        <v>110</v>
+      </c>
+      <c r="C192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B193" s="2">
+        <v>111</v>
+      </c>
+      <c r="C193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B194" s="2">
+        <v>112</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B195" s="2">
+        <v>113</v>
+      </c>
+      <c r="C195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B196" s="2">
+        <v>114</v>
+      </c>
+      <c r="C196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B197" s="2">
+        <v>115</v>
+      </c>
+      <c r="C197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B198" s="2">
+        <v>116</v>
+      </c>
+      <c r="C198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B199" s="2">
+        <v>117</v>
+      </c>
+      <c r="C199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B200" s="2">
+        <v>118</v>
+      </c>
+      <c r="C200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B201" s="2">
+        <v>119</v>
+      </c>
+      <c r="C201">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B202" s="2">
+        <v>120</v>
+      </c>
+      <c r="C202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B203" s="2">
+        <v>121</v>
+      </c>
+      <c r="C203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B204" s="2">
+        <v>122</v>
+      </c>
+      <c r="C204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B205" s="2">
+        <v>123</v>
+      </c>
+      <c r="C205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B206" s="2">
+        <v>124</v>
+      </c>
+      <c r="C206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B207" s="2">
+        <v>125</v>
+      </c>
+      <c r="C207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B208" s="2">
+        <v>126</v>
+      </c>
+      <c r="C208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B209" s="2">
+        <v>127</v>
+      </c>
+      <c r="C209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B210" s="2">
+        <v>130</v>
+      </c>
+      <c r="C210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B211" s="2">
+        <v>131</v>
+      </c>
+      <c r="C211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B212" s="2">
+        <v>132</v>
+      </c>
+      <c r="C212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B213" s="2">
+        <v>133</v>
+      </c>
+      <c r="C213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B214" s="2">
+        <v>134</v>
+      </c>
+      <c r="C214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B215" s="2">
+        <v>135</v>
+      </c>
+      <c r="C215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B216" s="2">
+        <v>136</v>
+      </c>
+      <c r="C216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B217" s="2">
+        <v>137</v>
+      </c>
+      <c r="C217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B218" s="2">
+        <v>138</v>
+      </c>
+      <c r="C218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B219" s="2">
+        <v>139</v>
+      </c>
+      <c r="C219">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B220" s="2">
+        <v>140</v>
+      </c>
+      <c r="C220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B221" s="2">
+        <v>141</v>
+      </c>
+      <c r="C221">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B222" s="2">
+        <v>142</v>
+      </c>
+      <c r="C222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B223" s="2">
+        <v>143</v>
+      </c>
+      <c r="C223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B224" s="2">
+        <v>144</v>
+      </c>
+      <c r="C224">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B225" s="2">
+        <v>145</v>
+      </c>
+      <c r="C225">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B226" s="2">
+        <v>146</v>
+      </c>
+      <c r="C226">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B227" s="2">
+        <v>147</v>
+      </c>
+      <c r="C227">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B228" s="2">
+        <v>148</v>
+      </c>
+      <c r="C228">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B229" s="2">
+        <v>149</v>
+      </c>
+      <c r="C229">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B230" s="2">
+        <v>150</v>
+      </c>
+      <c r="C230">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B231" s="2">
+        <v>151</v>
+      </c>
+      <c r="C231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B232" s="2">
+        <v>152</v>
+      </c>
+      <c r="C232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B233" s="2">
+        <v>153</v>
+      </c>
+      <c r="C233">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B234" s="2">
+        <v>154</v>
+      </c>
+      <c r="C234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B235" s="2">
+        <v>155</v>
+      </c>
+      <c r="C235">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B236" s="2">
+        <v>156</v>
+      </c>
+      <c r="C236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B237" s="2">
+        <v>157</v>
+      </c>
+      <c r="C237">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B238" s="2">
+        <v>158</v>
+      </c>
+      <c r="C238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B239" s="2">
+        <v>159</v>
+      </c>
+      <c r="C239">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B240" s="2">
+        <v>162</v>
+      </c>
+      <c r="C240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B241" s="2">
+        <v>163</v>
+      </c>
+      <c r="C241">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B242" s="2">
+        <v>164</v>
+      </c>
+      <c r="C242">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B243" s="2">
+        <v>165</v>
+      </c>
+      <c r="C243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B244" s="2">
+        <v>166</v>
+      </c>
+      <c r="C244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B245" s="2">
+        <v>167</v>
+      </c>
+      <c r="C245">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B246" s="2">
+        <v>168</v>
+      </c>
+      <c r="C246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B247" s="2">
+        <v>169</v>
+      </c>
+      <c r="C247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B248" s="2">
+        <v>170</v>
+      </c>
+      <c r="C248">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B249" s="2">
+        <v>171</v>
+      </c>
+      <c r="C249">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B250" s="2">
+        <v>174</v>
+      </c>
+      <c r="C250">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B251" s="2">
+        <v>175</v>
+      </c>
+      <c r="C251">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B252" s="2">
+        <v>176</v>
+      </c>
+      <c r="C252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B253" s="2">
+        <v>177</v>
+      </c>
+      <c r="C253">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B254" s="2">
+        <v>178</v>
+      </c>
+      <c r="C254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B255" s="2">
+        <v>179</v>
+      </c>
+      <c r="C255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B256" s="2">
+        <v>180</v>
+      </c>
+      <c r="C256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B257" s="2">
+        <v>181</v>
+      </c>
+      <c r="C257">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B258" s="2">
+        <v>182</v>
+      </c>
+      <c r="C258">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B259" s="2">
+        <v>183</v>
+      </c>
+      <c r="C259">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B260" s="2">
+        <v>184</v>
+      </c>
+      <c r="C260">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B261" s="2">
+        <v>185</v>
+      </c>
+      <c r="C261">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B262" s="2">
+        <v>186</v>
+      </c>
+      <c r="C262">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B263" s="2">
+        <v>187</v>
+      </c>
+      <c r="C263">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B264" s="2">
+        <v>190</v>
+      </c>
+      <c r="C264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B265" s="2">
+        <v>191</v>
+      </c>
+      <c r="C265">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B266" s="2">
+        <v>192</v>
+      </c>
+      <c r="C266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B267" s="2">
+        <v>193</v>
+      </c>
+      <c r="C267">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B268" s="2">
+        <v>194</v>
+      </c>
+      <c r="C268">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B269" s="2">
+        <v>195</v>
+      </c>
+      <c r="C269">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B270" s="2">
+        <v>196</v>
+      </c>
+      <c r="C270">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B271" s="2">
+        <v>198</v>
+      </c>
+      <c r="C271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B272" s="2">
+        <v>201</v>
+      </c>
+      <c r="C272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B273" s="2">
+        <v>202</v>
+      </c>
+      <c r="C273">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B274" s="2">
+        <v>203</v>
+      </c>
+      <c r="C274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B275" s="2">
+        <v>204</v>
+      </c>
+      <c r="C275">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B276" s="2">
+        <v>205</v>
+      </c>
+      <c r="C276">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B277" s="2">
+        <v>206</v>
+      </c>
+      <c r="C277">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B278" s="2">
+        <v>207</v>
+      </c>
+      <c r="C278">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B279" s="2">
+        <v>208</v>
+      </c>
+      <c r="C279">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B280" s="2">
+        <v>209</v>
+      </c>
+      <c r="C280">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B281" s="2">
+        <v>210</v>
+      </c>
+      <c r="C281">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B282" s="2">
+        <v>211</v>
+      </c>
+      <c r="C282">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B283" s="2">
+        <v>212</v>
+      </c>
+      <c r="C283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B284" s="2">
+        <v>213</v>
+      </c>
+      <c r="C284">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B285" s="2">
+        <v>214</v>
+      </c>
+      <c r="C285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B286" s="2">
+        <v>215</v>
+      </c>
+      <c r="C286">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B287" s="2">
+        <v>216</v>
+      </c>
+      <c r="C287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B288" s="2">
+        <v>217</v>
+      </c>
+      <c r="C288">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B289" s="2">
+        <v>218</v>
+      </c>
+      <c r="C289">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B290" s="2">
+        <v>219</v>
+      </c>
+      <c r="C290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B291" s="2">
+        <v>220</v>
+      </c>
+      <c r="C291">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B292" s="2">
+        <v>221</v>
+      </c>
+      <c r="C292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B293" s="2">
+        <v>222</v>
+      </c>
+      <c r="C293">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B294" s="2">
+        <v>223</v>
+      </c>
+      <c r="C294">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B295" s="2">
+        <v>224</v>
+      </c>
+      <c r="C295">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B296" s="2">
+        <v>225</v>
+      </c>
+      <c r="C296">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B297" s="2">
+        <v>226</v>
+      </c>
+      <c r="C297">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B298" s="2">
+        <v>227</v>
+      </c>
+      <c r="C298">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B299" s="2">
+        <v>228</v>
+      </c>
+      <c r="C299">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B300" s="2">
+        <v>229</v>
+      </c>
+      <c r="C300">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B301" s="2">
+        <v>230</v>
+      </c>
+      <c r="C301">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B302" s="2">
+        <v>231</v>
+      </c>
+      <c r="C302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B303" s="2">
+        <v>232</v>
+      </c>
+      <c r="C303">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B304" s="2">
+        <v>233</v>
+      </c>
+      <c r="C304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B305" s="2">
+        <v>234</v>
+      </c>
+      <c r="C305">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B306" s="2">
+        <v>237</v>
+      </c>
+      <c r="C306">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B307" s="2">
+        <v>238</v>
+      </c>
+      <c r="C307">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B308" s="2">
+        <v>239</v>
+      </c>
+      <c r="C308">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B309" s="2">
+        <v>240</v>
+      </c>
+      <c r="C309">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B310" s="2">
+        <v>241</v>
+      </c>
+      <c r="C310">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B311" s="2">
+        <v>242</v>
+      </c>
+      <c r="C311">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B312" s="2">
+        <v>243</v>
+      </c>
+      <c r="C312">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B313" s="2">
+        <v>244</v>
+      </c>
+      <c r="C313">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B314" s="2">
+        <v>245</v>
+      </c>
+      <c r="C314">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B315" s="2">
+        <v>246</v>
+      </c>
+      <c r="C315">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B316" s="2">
+        <v>247</v>
+      </c>
+      <c r="C316">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B317" s="2">
+        <v>248</v>
+      </c>
+      <c r="C317">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B318" s="2">
+        <v>249</v>
+      </c>
+      <c r="C318">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B319" s="2">
+        <v>250</v>
+      </c>
+      <c r="C319">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B320" s="2">
+        <v>251</v>
+      </c>
+      <c r="C320">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B321" s="2">
+        <v>252</v>
+      </c>
+      <c r="C321">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B322" s="2">
+        <v>253</v>
+      </c>
+      <c r="C322">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B323" s="2">
+        <v>254</v>
+      </c>
+      <c r="C323">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B324" s="2">
+        <v>255</v>
+      </c>
+      <c r="C324">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B325" s="2">
+        <v>256</v>
+      </c>
+      <c r="C325">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B326" s="2">
+        <v>257</v>
+      </c>
+      <c r="C326">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B327" s="2">
+        <v>260</v>
+      </c>
+      <c r="C327">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B328" s="2">
+        <v>261</v>
+      </c>
+      <c r="C328">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B329" s="2">
+        <v>262</v>
+      </c>
+      <c r="C329">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B330" s="2">
+        <v>263</v>
+      </c>
+      <c r="C330">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B331" s="2">
+        <v>264</v>
+      </c>
+      <c r="C331">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B332" s="2">
+        <v>265</v>
+      </c>
+      <c r="C332">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B333" s="2">
+        <v>266</v>
+      </c>
+      <c r="C333">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B334" s="2">
+        <v>267</v>
+      </c>
+      <c r="C334">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B335" s="2">
+        <v>268</v>
+      </c>
+      <c r="C335">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B336" s="2">
+        <v>269</v>
+      </c>
+      <c r="C336">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B337" s="2">
+        <v>270</v>
+      </c>
+      <c r="C337">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B338" s="2">
+        <v>271</v>
+      </c>
+      <c r="C338">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B339" s="2">
+        <v>272</v>
+      </c>
+      <c r="C339">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B340" s="2">
+        <v>273</v>
+      </c>
+      <c r="C340">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B341" s="2">
+        <v>274</v>
+      </c>
+      <c r="C341">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B342" s="2">
+        <v>275</v>
+      </c>
+      <c r="C342">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B343" s="2">
+        <v>276</v>
+      </c>
+      <c r="C343">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B344" s="2">
+        <v>277</v>
+      </c>
+      <c r="C344">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B345" s="2">
+        <v>278</v>
+      </c>
+      <c r="C345">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B346" s="2">
+        <v>279</v>
+      </c>
+      <c r="C346">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B347" s="2">
+        <v>280</v>
+      </c>
+      <c r="C347">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B348" s="2">
+        <v>281</v>
+      </c>
+      <c r="C348">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B349" s="2">
+        <v>282</v>
+      </c>
+      <c r="C349">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B350" s="2">
+        <v>285</v>
+      </c>
+      <c r="C350">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B351" s="2">
+        <v>286</v>
+      </c>
+      <c r="C351">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B352" s="2">
+        <v>287</v>
+      </c>
+      <c r="C352">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B353" s="2">
+        <v>288</v>
+      </c>
+      <c r="C353">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B354" s="2">
+        <v>289</v>
+      </c>
+      <c r="C354">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B355" s="2">
+        <v>290</v>
+      </c>
+      <c r="C355">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B356" s="2">
+        <v>291</v>
+      </c>
+      <c r="C356">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B357" s="2">
+        <v>292</v>
+      </c>
+      <c r="C357">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B358" s="2">
+        <v>293</v>
+      </c>
+      <c r="C358">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B359" s="2">
+        <v>294</v>
+      </c>
+      <c r="C359">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B360" s="2">
+        <v>295</v>
+      </c>
+      <c r="C360">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B361" s="2">
+        <v>296</v>
+      </c>
+      <c r="C361">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B362" s="2">
+        <v>297</v>
+      </c>
+      <c r="C362">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B363" s="2">
+        <v>300</v>
+      </c>
+      <c r="C363">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B364" s="2">
+        <v>301</v>
+      </c>
+      <c r="C364">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B365" s="2">
+        <v>302</v>
+      </c>
+      <c r="C365">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B366" s="2">
+        <v>303</v>
+      </c>
+      <c r="C366">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B367" s="2">
+        <v>304</v>
+      </c>
+      <c r="C367">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B368" s="2">
+        <v>305</v>
+      </c>
+      <c r="C368">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B369" s="2">
+        <v>306</v>
+      </c>
+      <c r="C369">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B370" s="2">
+        <v>310</v>
+      </c>
+      <c r="C370">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B371" s="2">
+        <v>311</v>
+      </c>
+      <c r="C371">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B372" s="2">
+        <v>312</v>
+      </c>
+      <c r="C372">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B373" s="2">
+        <v>318</v>
+      </c>
+      <c r="C373">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B374" s="2">
+        <v>323</v>
+      </c>
+      <c r="C374">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B375" s="2">
+        <v>324</v>
+      </c>
+      <c r="C375">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B376" s="2">
+        <v>325</v>
+      </c>
+      <c r="C376">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B377" s="2">
+        <v>326</v>
+      </c>
+      <c r="C377">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B378" s="2">
+        <v>327</v>
+      </c>
+      <c r="C378">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B379" s="2">
+        <v>331</v>
+      </c>
+      <c r="C379">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B380" s="2">
+        <v>332</v>
+      </c>
+      <c r="C380">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B381" s="2">
+        <v>333</v>
+      </c>
+      <c r="C381">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B382" s="2">
+        <v>334</v>
+      </c>
+      <c r="C382">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B383" s="2">
+        <v>335</v>
+      </c>
+      <c r="C383">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B384" s="2">
+        <v>336</v>
+      </c>
+      <c r="C384">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B385" s="2">
+        <v>337</v>
+      </c>
+      <c r="C385">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B386" s="2">
+        <v>338</v>
+      </c>
+      <c r="C386">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B387" s="2">
+        <v>339</v>
+      </c>
+      <c r="C387">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B388" s="2">
+        <v>340</v>
+      </c>
+      <c r="C388">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B389" s="2">
+        <v>341</v>
+      </c>
+      <c r="C389">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B390" s="2">
+        <v>342</v>
+      </c>
+      <c r="C390">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B391" s="2">
+        <v>343</v>
+      </c>
+      <c r="C391">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B392" s="2">
+        <v>344</v>
+      </c>
+      <c r="C392">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B393" s="2">
+        <v>345</v>
+      </c>
+      <c r="C393">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B394" s="2">
+        <v>346</v>
+      </c>
+      <c r="C394">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="395" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B395" s="2">
+        <v>347</v>
+      </c>
+      <c r="C395">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B396" s="2">
+        <v>348</v>
+      </c>
+      <c r="C396">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B397" s="2">
+        <v>349</v>
+      </c>
+      <c r="C397">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="398" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B398" s="2">
+        <v>350</v>
+      </c>
+      <c r="C398">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="399" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B399" s="2">
+        <v>351</v>
+      </c>
+      <c r="C399">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B400" s="2">
+        <v>352</v>
+      </c>
+      <c r="C400">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B401" s="2">
+        <v>353</v>
+      </c>
+      <c r="C401">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B402" s="2">
+        <v>354</v>
+      </c>
+      <c r="C402">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B403" s="2">
+        <v>355</v>
+      </c>
+      <c r="C403">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B404" s="2">
+        <v>356</v>
+      </c>
+      <c r="C404">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B405" s="2">
+        <v>357</v>
+      </c>
+      <c r="C405">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B406" s="2">
+        <v>358</v>
+      </c>
+      <c r="C406">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B407" s="2">
+        <v>359</v>
+      </c>
+      <c r="C407">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B408" s="2">
+        <v>360</v>
+      </c>
+      <c r="C408">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B409" s="2">
+        <v>361</v>
+      </c>
+      <c r="C409">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="410" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B410" s="2">
+        <v>362</v>
+      </c>
+      <c r="C410">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B411" s="2">
+        <v>363</v>
+      </c>
+      <c r="C411">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B412" s="2">
+        <v>364</v>
+      </c>
+      <c r="C412">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B413" s="2">
+        <v>365</v>
+      </c>
+      <c r="C413">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="414" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B414" s="2">
+        <v>366</v>
+      </c>
+      <c r="C414">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B415" s="2">
+        <v>367</v>
+      </c>
+      <c r="C415">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B416" s="2">
+        <v>368</v>
+      </c>
+      <c r="C416">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B417" s="2">
+        <v>369</v>
+      </c>
+      <c r="C417">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B418" s="2">
+        <v>370</v>
+      </c>
+      <c r="C418">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B419" s="2">
+        <v>371</v>
+      </c>
+      <c r="C419">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="420" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B420" s="2">
+        <v>372</v>
+      </c>
+      <c r="C420">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B421" s="2">
+        <v>373</v>
+      </c>
+      <c r="C421">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B422" s="2">
+        <v>374</v>
+      </c>
+      <c r="C422">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B423" s="2">
+        <v>379</v>
+      </c>
+      <c r="C423">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B424" s="2">
+        <v>381</v>
+      </c>
+      <c r="C424">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="425" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B425" s="2">
+        <v>382</v>
+      </c>
+      <c r="C425">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B426" s="2">
+        <v>385</v>
+      </c>
+      <c r="C426">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="427" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B427" s="2">
+        <v>386</v>
+      </c>
+      <c r="C427">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B428" s="2">
+        <v>395</v>
+      </c>
+      <c r="C428">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="429" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B429" s="2">
+        <v>396</v>
+      </c>
+      <c r="C429">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="430" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B430" s="2">
+        <v>397</v>
+      </c>
+      <c r="C430">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B431" s="2">
+        <v>398</v>
+      </c>
+      <c r="C431">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B432" s="2">
+        <v>399</v>
+      </c>
+      <c r="C432">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="433" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B433" s="2">
+        <v>400</v>
+      </c>
+      <c r="C433">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B434" s="2">
+        <v>401</v>
+      </c>
+      <c r="C434">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B435" s="2">
+        <v>402</v>
+      </c>
+      <c r="C435">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B436" s="2">
+        <v>404</v>
+      </c>
+      <c r="C436">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B437" s="2">
+        <v>408</v>
+      </c>
+      <c r="C437">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B438" s="2">
+        <v>409</v>
+      </c>
+      <c r="C438">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B439" s="2">
+        <v>410</v>
+      </c>
+      <c r="C439">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="440" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B440" s="2">
+        <v>411</v>
+      </c>
+      <c r="C440">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="441" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B441" s="2">
+        <v>415</v>
+      </c>
+      <c r="C441">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="442" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B442" s="2">
+        <v>416</v>
+      </c>
+      <c r="C442">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="443" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B443" s="2">
+        <v>417</v>
+      </c>
+      <c r="C443">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B444" s="2">
+        <v>418</v>
+      </c>
+      <c r="C444">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="445" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B445" s="2">
+        <v>420</v>
+      </c>
+      <c r="C445">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="446" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B446" s="2">
+        <v>421</v>
+      </c>
+      <c r="C446">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="447" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B447" s="2">
+        <v>423</v>
+      </c>
+      <c r="C447">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="448" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B448" s="2">
+        <v>426</v>
+      </c>
+      <c r="C448">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="449" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B449" s="2">
+        <v>428</v>
+      </c>
+      <c r="C449">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="450" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B450" s="2">
+        <v>429</v>
+      </c>
+      <c r="C450">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="451" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B451" s="2">
+        <v>430</v>
+      </c>
+      <c r="C451">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B452" s="2">
+        <v>431</v>
+      </c>
+      <c r="C452">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="453" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B453" s="2">
+        <v>432</v>
+      </c>
+      <c r="C453">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="454" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B454" s="2">
+        <v>433</v>
+      </c>
+      <c r="C454">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="455" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B455" s="2">
+        <v>434</v>
+      </c>
+      <c r="C455">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B456" s="2">
+        <v>435</v>
+      </c>
+      <c r="C456">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="457" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B457" s="2">
+        <v>436</v>
+      </c>
+      <c r="C457">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="458" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B458" s="2">
+        <v>437</v>
+      </c>
+      <c r="C458">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="459" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B459" s="2">
+        <v>438</v>
+      </c>
+      <c r="C459">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="460" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B460" s="2">
+        <v>439</v>
+      </c>
+      <c r="C460">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="461" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B461" s="2">
+        <v>440</v>
+      </c>
+      <c r="C461">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="462" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B462" s="2">
+        <v>441</v>
+      </c>
+      <c r="C462">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="463" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B463" s="2">
+        <v>442</v>
+      </c>
+      <c r="C463">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="464" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B464" s="2">
+        <v>443</v>
+      </c>
+      <c r="C464">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="465" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B465" s="2">
+        <v>445</v>
+      </c>
+      <c r="C465">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="466" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B466" s="2">
+        <v>446</v>
+      </c>
+      <c r="C466">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="467" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B467" s="2">
+        <v>447</v>
+      </c>
+      <c r="C467">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="468" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B468" s="2">
+        <v>452</v>
+      </c>
+      <c r="C468">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="469" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B469" s="2">
+        <v>453</v>
+      </c>
+      <c r="C469">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="470" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B470" s="2">
+        <v>454</v>
+      </c>
+      <c r="C470">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="471" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B471" s="2">
+        <v>455</v>
+      </c>
+      <c r="C471">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="472" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B472" s="2">
+        <v>456</v>
+      </c>
+      <c r="C472">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="473" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B473" s="2">
+        <v>457</v>
+      </c>
+      <c r="C473">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B474" s="2">
+        <v>458</v>
+      </c>
+      <c r="C474">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B475" s="2">
+        <v>459</v>
+      </c>
+      <c r="C475">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="476" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B476" s="2">
+        <v>460</v>
+      </c>
+      <c r="C476">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="477" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B477" s="2">
+        <v>461</v>
+      </c>
+      <c r="C477">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="478" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B478" s="2">
+        <v>462</v>
+      </c>
+      <c r="C478">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B479" s="2">
+        <v>463</v>
+      </c>
+      <c r="C479">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="480" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B480" s="2">
+        <v>464</v>
+      </c>
+      <c r="C480">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B481" s="2">
+        <v>465</v>
+      </c>
+      <c r="C481">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="482" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B482" s="2">
+        <v>466</v>
+      </c>
+      <c r="C482">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="483" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B483" s="2">
+        <v>467</v>
+      </c>
+      <c r="C483">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="484" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B484" s="2">
+        <v>468</v>
+      </c>
+      <c r="C484">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="485" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B485" s="2">
+        <v>469</v>
+      </c>
+      <c r="C485">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="486" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B486" s="2">
+        <v>470</v>
+      </c>
+      <c r="C486">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="487" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B487" s="2">
+        <v>471</v>
+      </c>
+      <c r="C487">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="488" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B488" s="2">
+        <v>472</v>
+      </c>
+      <c r="C488">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="489" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B489" s="2">
+        <v>473</v>
+      </c>
+      <c r="C489">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="490" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B490" s="2">
+        <v>474</v>
+      </c>
+      <c r="C490">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="491" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B491" s="2">
+        <v>475</v>
+      </c>
+      <c r="C491">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="492" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B492" s="2">
+        <v>476</v>
+      </c>
+      <c r="C492">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="493" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B493" s="2">
+        <v>477</v>
+      </c>
+      <c r="C493">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="494" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B494" s="2">
+        <v>478</v>
+      </c>
+      <c r="C494">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="495" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B495" s="2">
+        <v>479</v>
+      </c>
+      <c r="C495">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="496" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B496" s="2">
+        <v>480</v>
+      </c>
+      <c r="C496">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="497" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B497" s="2">
+        <v>481</v>
+      </c>
+      <c r="C497">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="498" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B498" s="2">
+        <v>482</v>
+      </c>
+      <c r="C498">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="499" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B499" s="2">
+        <v>485</v>
+      </c>
+      <c r="C499">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="500" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B500" s="2">
+        <v>486</v>
+      </c>
+      <c r="C500">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="501" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B501" s="2">
+        <v>490</v>
+      </c>
+      <c r="C501">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="502" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B502" s="2">
+        <v>491</v>
+      </c>
+      <c r="C502">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="503" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B503" s="2">
+        <v>492</v>
+      </c>
+      <c r="C503">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="504" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B504" s="2">
+        <v>493</v>
+      </c>
+      <c r="C504">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="505" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B505" s="2">
+        <v>494</v>
+      </c>
+      <c r="C505">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="506" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B506" s="2">
+        <v>495</v>
+      </c>
+      <c r="C506">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="507" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B507" s="2">
+        <v>496</v>
+      </c>
+      <c r="C507">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="508" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B508" s="2">
+        <v>497</v>
+      </c>
+      <c r="C508">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="509" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B509" s="2">
+        <v>498</v>
+      </c>
+      <c r="C509">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="510" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B510" s="2">
+        <v>499</v>
+      </c>
+      <c r="C510">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="511" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B511" s="2">
+        <v>502</v>
+      </c>
+      <c r="C511">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="512" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B512" s="2">
+        <v>503</v>
+      </c>
+      <c r="C512">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="513" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B513" s="2">
+        <v>506</v>
+      </c>
+      <c r="C513">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="514" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B514" s="2">
+        <v>507</v>
+      </c>
+      <c r="C514">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="515" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B515" s="2">
+        <v>508</v>
+      </c>
+      <c r="C515">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="516" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B516" s="2">
+        <v>509</v>
+      </c>
+      <c r="C516">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="517" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B517" s="2">
+        <v>510</v>
+      </c>
+      <c r="C517">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="518" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B518" s="2">
+        <v>515</v>
+      </c>
+      <c r="C518">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="519" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B519" s="2">
+        <v>516</v>
+      </c>
+      <c r="C519">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="520" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B520" s="2">
+        <v>517</v>
+      </c>
+      <c r="C520">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="521" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B521" s="2">
+        <v>518</v>
+      </c>
+      <c r="C521">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="522" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B522" s="2">
+        <v>519</v>
+      </c>
+      <c r="C522">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="523" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B523" s="2">
+        <v>520</v>
+      </c>
+      <c r="C523">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="524" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B524" s="2">
+        <v>521</v>
+      </c>
+      <c r="C524">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="525" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B525" s="2">
+        <v>522</v>
+      </c>
+      <c r="C525">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="526" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B526" s="2">
+        <v>523</v>
+      </c>
+      <c r="C526">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="527" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B527" s="2">
+        <v>524</v>
+      </c>
+      <c r="C527">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="528" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B528" s="2">
+        <v>525</v>
+      </c>
+      <c r="C528">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="529" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B529" s="2">
+        <v>526</v>
+      </c>
+      <c r="C529">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="530" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B530" s="2">
+        <v>530</v>
+      </c>
+      <c r="C530">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="531" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B531" s="2">
+        <v>531</v>
+      </c>
+      <c r="C531">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="532" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B532" s="2">
+        <v>532</v>
+      </c>
+      <c r="C532">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="533" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B533" s="2">
+        <v>533</v>
+      </c>
+      <c r="C533">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="534" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B534" s="2">
+        <v>534</v>
+      </c>
+      <c r="C534">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="535" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B535" s="2">
+        <v>535</v>
+      </c>
+      <c r="C535">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="536" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B536" s="2">
+        <v>536</v>
+      </c>
+      <c r="C536">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="537" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B537" s="2">
+        <v>537</v>
+      </c>
+      <c r="C537">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="538" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B538" s="2">
+        <v>538</v>
+      </c>
+      <c r="C538">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="539" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B539" s="2">
+        <v>539</v>
+      </c>
+      <c r="C539">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="540" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B540" s="2">
+        <v>540</v>
+      </c>
+      <c r="C540">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="541" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B541" s="2">
+        <v>543</v>
+      </c>
+      <c r="C541">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="542" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B542" s="2">
+        <v>544</v>
+      </c>
+      <c r="C542">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="543" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B543" s="2">
+        <v>545</v>
+      </c>
+      <c r="C543">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="544" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B544" s="2">
+        <v>546</v>
+      </c>
+      <c r="C544">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="545" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B545" s="2">
+        <v>547</v>
+      </c>
+      <c r="C545">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="546" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B546" s="2">
+        <v>548</v>
+      </c>
+      <c r="C546">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="547" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B547" s="2">
+        <v>549</v>
+      </c>
+      <c r="C547">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="548" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B548" s="2">
+        <v>550</v>
+      </c>
+      <c r="C548">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="549" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B549" s="2">
+        <v>551</v>
+      </c>
+      <c r="C549">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="550" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B550" s="2">
+        <v>552</v>
+      </c>
+      <c r="C550">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="551" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B551" s="2">
+        <v>553</v>
+      </c>
+      <c r="C551">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="552" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B552" s="2">
+        <v>554</v>
+      </c>
+      <c r="C552">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="553" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B553" s="2">
+        <v>555</v>
+      </c>
+      <c r="C553">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="554" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B554" s="2">
+        <v>556</v>
+      </c>
+      <c r="C554">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="555" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B555" s="2">
+        <v>557</v>
+      </c>
+      <c r="C555">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="556" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B556" s="2">
+        <v>558</v>
+      </c>
+      <c r="C556">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="557" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B557" s="2">
+        <v>559</v>
+      </c>
+      <c r="C557">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="558" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B558" s="2">
+        <v>560</v>
+      </c>
+      <c r="C558">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="559" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B559" s="2">
+        <v>561</v>
+      </c>
+      <c r="C559">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="560" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B560" s="2">
+        <v>562</v>
+      </c>
+      <c r="C560">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="561" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B561" s="2">
+        <v>563</v>
+      </c>
+      <c r="C561">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="562" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B562" s="2">
+        <v>564</v>
+      </c>
+      <c r="C562">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="563" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B563" s="2">
+        <v>565</v>
+      </c>
+      <c r="C563">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="564" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B564" s="2">
+        <v>566</v>
+      </c>
+      <c r="C564">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="565" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B565" s="2">
+        <v>567</v>
+      </c>
+      <c r="C565">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="566" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B566" s="2">
+        <v>568</v>
+      </c>
+      <c r="C566">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="567" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B567" s="2">
+        <v>569</v>
+      </c>
+      <c r="C567">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="568" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B568" s="2">
+        <v>570</v>
+      </c>
+      <c r="C568">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="569" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B569" s="2">
+        <v>571</v>
+      </c>
+      <c r="C569">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="570" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B570" s="2">
+        <v>572</v>
+      </c>
+      <c r="C570">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="571" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B571" s="2">
+        <v>573</v>
+      </c>
+      <c r="C571">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="572" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B572" s="2">
+        <v>574</v>
+      </c>
+      <c r="C572">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="573" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B573" s="2">
+        <v>575</v>
+      </c>
+      <c r="C573">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="574" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B574" s="2">
+        <v>579</v>
+      </c>
+      <c r="C574">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="575" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B575" s="2">
+        <v>580</v>
+      </c>
+      <c r="C575">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="576" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B576" s="2">
+        <v>581</v>
+      </c>
+      <c r="C576">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="577" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B577" s="2">
+        <v>582</v>
+      </c>
+      <c r="C577">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="578" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B578" s="2">
+        <v>583</v>
+      </c>
+      <c r="C578">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="579" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B579" s="2">
+        <v>584</v>
+      </c>
+      <c r="C579">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="580" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B580" s="2">
+        <v>585</v>
+      </c>
+      <c r="C580">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="581" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B581" s="2">
+        <v>586</v>
+      </c>
+      <c r="C581">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="582" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B582" s="2">
+        <v>587</v>
+      </c>
+      <c r="C582">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="583" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B583" s="2">
+        <v>588</v>
+      </c>
+      <c r="C583">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="584" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B584" s="2">
+        <v>589</v>
+      </c>
+      <c r="C584">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="585" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B585" s="2">
+        <v>590</v>
+      </c>
+      <c r="C585">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="586" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B586" s="2">
+        <v>591</v>
+      </c>
+      <c r="C586">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="587" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B587" s="2">
+        <v>592</v>
+      </c>
+      <c r="C587">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="588" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B588" s="2">
+        <v>593</v>
+      </c>
+      <c r="C588">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="589" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B589" s="2">
+        <v>594</v>
+      </c>
+      <c r="C589">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="590" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B590" s="2">
+        <v>595</v>
+      </c>
+      <c r="C590">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="591" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B591" s="2">
+        <v>596</v>
+      </c>
+      <c r="C591">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="592" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B592" s="2">
+        <v>597</v>
+      </c>
+      <c r="C592">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="593" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B593" s="2">
+        <v>598</v>
+      </c>
+      <c r="C593">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="594" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B594" s="2">
+        <v>605</v>
+      </c>
+      <c r="C594">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="595" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B595" s="2">
+        <v>606</v>
+      </c>
+      <c r="C595">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="596" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B596" s="2">
+        <v>607</v>
+      </c>
+      <c r="C596">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="597" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B597" s="2">
+        <v>608</v>
+      </c>
+      <c r="C597">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="598" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B598" s="2">
+        <v>609</v>
+      </c>
+      <c r="C598">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="599" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B599" s="2">
+        <v>610</v>
+      </c>
+      <c r="C599">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="600" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B600" s="2">
+        <v>611</v>
+      </c>
+      <c r="C600">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="601" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B601" s="2">
+        <v>612</v>
+      </c>
+      <c r="C601">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="602" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B602" s="2">
+        <v>613</v>
+      </c>
+      <c r="C602">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="603" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B603" s="2">
+        <v>614</v>
+      </c>
+      <c r="C603">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="604" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B604" s="2">
+        <v>615</v>
+      </c>
+      <c r="C604">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="605" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B605" s="2">
+        <v>616</v>
+      </c>
+      <c r="C605">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="606" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B606" s="2">
+        <v>617</v>
+      </c>
+      <c r="C606">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="607" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B607" s="2">
+        <v>621</v>
+      </c>
+      <c r="C607">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="608" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B608" s="2">
+        <v>622</v>
+      </c>
+      <c r="C608">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="609" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B609" s="2">
+        <v>627</v>
+      </c>
+      <c r="C609">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="610" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B610" s="2">
+        <v>628</v>
+      </c>
+      <c r="C610">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="611" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B611" s="2">
+        <v>629</v>
+      </c>
+      <c r="C611">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="612" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B612" s="2">
+        <v>630</v>
+      </c>
+      <c r="C612">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="613" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B613" s="2">
+        <v>631</v>
+      </c>
+      <c r="C613">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="614" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B614" s="2">
+        <v>632</v>
+      </c>
+      <c r="C614">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="615" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B615" s="2">
+        <v>633</v>
+      </c>
+      <c r="C615">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="616" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B616" s="2">
+        <v>634</v>
+      </c>
+      <c r="C616">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="617" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B617" s="2">
+        <v>635</v>
+      </c>
+      <c r="C617">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="618" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B618" s="2">
+        <v>636</v>
+      </c>
+      <c r="C618">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="619" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B619" s="2">
+        <v>639</v>
+      </c>
+      <c r="C619">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="620" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B620" s="2">
+        <v>640</v>
+      </c>
+      <c r="C620">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="621" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B621" s="2">
+        <v>641</v>
+      </c>
+      <c r="C621">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="622" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B622" s="2">
+        <v>642</v>
+      </c>
+      <c r="C622">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="623" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B623" s="2">
+        <v>643</v>
+      </c>
+      <c r="C623">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="624" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B624" s="2">
+        <v>644</v>
+      </c>
+      <c r="C624">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="625" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B625" s="2">
+        <v>645</v>
+      </c>
+      <c r="C625">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="626" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B626" s="2">
+        <v>646</v>
+      </c>
+      <c r="C626">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="627" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B627" s="2">
+        <v>647</v>
+      </c>
+      <c r="C627">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="628" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B628" s="2">
+        <v>648</v>
+      </c>
+      <c r="C628">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="629" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B629" s="2">
+        <v>649</v>
+      </c>
+      <c r="C629">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="630" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B630" s="2">
+        <v>650</v>
+      </c>
+      <c r="C630">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="631" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B631" s="2">
+        <v>651</v>
+      </c>
+      <c r="C631">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="632" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B632" s="2">
+        <v>652</v>
+      </c>
+      <c r="C632">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="633" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B633" s="2">
+        <v>653</v>
+      </c>
+      <c r="C633">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="634" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B634" s="2">
+        <v>654</v>
+      </c>
+      <c r="C634">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="635" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B635" s="2">
+        <v>655</v>
+      </c>
+      <c r="C635">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="636" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B636" s="2">
+        <v>656</v>
+      </c>
+      <c r="C636">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="637" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B637" s="2">
+        <v>657</v>
+      </c>
+      <c r="C637">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="638" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B638" s="2">
+        <v>658</v>
+      </c>
+      <c r="C638">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="639" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B639" s="2">
+        <v>659</v>
+      </c>
+      <c r="C639">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="640" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B640" s="2">
+        <v>660</v>
+      </c>
+      <c r="C640">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="641" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B641" s="2">
+        <v>661</v>
+      </c>
+      <c r="C641">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="642" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B642" s="2">
+        <v>662</v>
+      </c>
+      <c r="C642">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="643" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B643" s="2">
+        <v>663</v>
+      </c>
+      <c r="C643">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="644" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B644" s="2">
+        <v>667</v>
+      </c>
+      <c r="C644">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="645" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B645" s="2">
+        <v>668</v>
+      </c>
+      <c r="C645">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="646" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B646" s="2">
+        <v>669</v>
+      </c>
+      <c r="C646">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="647" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B647" s="2">
+        <v>670</v>
+      </c>
+      <c r="C647">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="648" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B648" s="2">
+        <v>671</v>
+      </c>
+      <c r="C648">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="649" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B649" s="2">
+        <v>672</v>
+      </c>
+      <c r="C649">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="650" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B650" s="2">
+        <v>673</v>
+      </c>
+      <c r="C650">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="651" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B651" s="2">
+        <v>674</v>
+      </c>
+      <c r="C651">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="652" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B652" s="2">
+        <v>675</v>
+      </c>
+      <c r="C652">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="653" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B653" s="2">
+        <v>676</v>
+      </c>
+      <c r="C653">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="654" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B654" s="2">
+        <v>677</v>
+      </c>
+      <c r="C654">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="655" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B655" s="2">
+        <v>678</v>
+      </c>
+      <c r="C655">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="656" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B656" s="2">
+        <v>679</v>
+      </c>
+      <c r="C656">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="657" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B657" s="2">
+        <v>680</v>
+      </c>
+      <c r="C657">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="658" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B658" s="2">
+        <v>681</v>
+      </c>
+      <c r="C658">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="659" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B659" s="2">
+        <v>682</v>
+      </c>
+      <c r="C659">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="660" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B660" s="2">
+        <v>683</v>
+      </c>
+      <c r="C660">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="661" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B661" s="2">
+        <v>684</v>
+      </c>
+      <c r="C661">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="662" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B662" s="2">
+        <v>685</v>
+      </c>
+      <c r="C662">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="663" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B663" s="2">
+        <v>686</v>
+      </c>
+      <c r="C663">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="664" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B664" s="2">
+        <v>687</v>
+      </c>
+      <c r="C664">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="665" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B665" s="2">
+        <v>688</v>
+      </c>
+      <c r="C665">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="666" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B666" s="2">
+        <v>689</v>
+      </c>
+      <c r="C666">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="667" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B667" s="2">
+        <v>690</v>
+      </c>
+      <c r="C667">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="668" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B668" s="2">
+        <v>691</v>
+      </c>
+      <c r="C668">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="669" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B669" s="2">
+        <v>694</v>
+      </c>
+      <c r="C669">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="670" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B670" s="2">
+        <v>695</v>
+      </c>
+      <c r="C670">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="671" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B671" s="2">
+        <v>696</v>
+      </c>
+      <c r="C671">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="672" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B672" s="2">
+        <v>697</v>
+      </c>
+      <c r="C672">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="673" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B673" s="2">
+        <v>698</v>
+      </c>
+      <c r="C673">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="674" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B674" s="2">
+        <v>699</v>
+      </c>
+      <c r="C674">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="675" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B675" s="2">
+        <v>700</v>
+      </c>
+      <c r="C675">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="676" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B676" s="2">
+        <v>701</v>
+      </c>
+      <c r="C676">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="677" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B677" s="2">
+        <v>702</v>
+      </c>
+      <c r="C677">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="678" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B678" s="2">
+        <v>703</v>
+      </c>
+      <c r="C678">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="679" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B679" s="2">
+        <v>704</v>
+      </c>
+      <c r="C679">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="680" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B680" s="2">
+        <v>705</v>
+      </c>
+      <c r="C680">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="681" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B681" s="2">
+        <v>706</v>
+      </c>
+      <c r="C681">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="682" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B682" s="2">
+        <v>707</v>
+      </c>
+      <c r="C682">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="683" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B683" s="2">
+        <v>708</v>
+      </c>
+      <c r="C683">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="684" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B684" s="2">
+        <v>709</v>
+      </c>
+      <c r="C684">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="685" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B685" s="2">
+        <v>710</v>
+      </c>
+      <c r="C685">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="686" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B686" s="2">
+        <v>713</v>
+      </c>
+      <c r="C686">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="687" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B687" s="2">
+        <v>718</v>
+      </c>
+      <c r="C687">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="688" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B688" s="2">
+        <v>719</v>
+      </c>
+      <c r="C688">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="689" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B689" s="2">
+        <v>720</v>
+      </c>
+      <c r="C689">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="690" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B690" s="2">
+        <v>721</v>
+      </c>
+      <c r="C690">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="691" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B691" s="2">
+        <v>722</v>
+      </c>
+      <c r="C691">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="692" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B692" s="2">
+        <v>723</v>
+      </c>
+      <c r="C692">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="693" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B693" s="2">
+        <v>724</v>
+      </c>
+      <c r="C693">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="694" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B694" s="2">
+        <v>725</v>
+      </c>
+      <c r="C694">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="695" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B695" s="2">
+        <v>726</v>
+      </c>
+      <c r="C695">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="696" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B696" s="2">
+        <v>728</v>
+      </c>
+      <c r="C696">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="697" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B697" s="2">
+        <v>738</v>
+      </c>
+      <c r="C697">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="698" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B698" s="2">
+        <v>739</v>
+      </c>
+      <c r="C698">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="699" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B699" s="2">
+        <v>740</v>
+      </c>
+      <c r="C699">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="700" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B700" s="2">
+        <v>741</v>
+      </c>
+      <c r="C700">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="701" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B701" s="2">
+        <v>742</v>
+      </c>
+      <c r="C701">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="702" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B702" s="2">
+        <v>743</v>
+      </c>
+      <c r="C702">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="703" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B703" s="2">
+        <v>744</v>
+      </c>
+      <c r="C703">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="704" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B704" s="2">
+        <v>745</v>
+      </c>
+      <c r="C704">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="705" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B705" s="2">
+        <v>746</v>
+      </c>
+      <c r="C705">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="706" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B706" s="2">
+        <v>747</v>
+      </c>
+      <c r="C706">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="707" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B707" s="2">
+        <v>748</v>
+      </c>
+      <c r="C707">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="708" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B708" s="2">
+        <v>751</v>
+      </c>
+      <c r="C708">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="709" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B709" s="2">
+        <v>754</v>
+      </c>
+      <c r="C709">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="710" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B710" s="2">
+        <v>757</v>
+      </c>
+      <c r="C710">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="711" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B711" s="2">
+        <v>758</v>
+      </c>
+      <c r="C711">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="712" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B712" s="2">
+        <v>759</v>
+      </c>
+      <c r="C712">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="713" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B713" s="2">
+        <v>760</v>
+      </c>
+      <c r="C713">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="714" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B714" s="2">
+        <v>761</v>
+      </c>
+      <c r="C714">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="715" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B715" s="2">
+        <v>762</v>
+      </c>
+      <c r="C715">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="716" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B716" s="2">
+        <v>763</v>
+      </c>
+      <c r="C716">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="717" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B717" s="2">
+        <v>766</v>
+      </c>
+      <c r="C717">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="718" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B718" s="2">
+        <v>767</v>
+      </c>
+      <c r="C718">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="719" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B719" s="2">
+        <v>768</v>
+      </c>
+      <c r="C719">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="720" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B720" s="2">
+        <v>769</v>
+      </c>
+      <c r="C720">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="721" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B721" s="2">
+        <v>770</v>
+      </c>
+      <c r="C721">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="722" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B722" s="2">
+        <v>771</v>
+      </c>
+      <c r="C722">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="723" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B723" s="2">
+        <v>772</v>
+      </c>
+      <c r="C723">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="724" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B724" s="2">
+        <v>773</v>
+      </c>
+      <c r="C724">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="725" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B725" s="2">
+        <v>774</v>
+      </c>
+      <c r="C725">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="726" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B726" s="2">
+        <v>775</v>
+      </c>
+      <c r="C726">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="727" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B727" s="2">
+        <v>776</v>
+      </c>
+      <c r="C727">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="728" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B728" s="2">
+        <v>779</v>
+      </c>
+      <c r="C728">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="729" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B729" s="2">
+        <v>780</v>
+      </c>
+      <c r="C729">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="730" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B730" s="2">
+        <v>781</v>
+      </c>
+      <c r="C730">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="731" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B731" s="2">
+        <v>782</v>
+      </c>
+      <c r="C731">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="732" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B732" s="2">
+        <v>783</v>
+      </c>
+      <c r="C732">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="733" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B733" s="2">
+        <v>784</v>
+      </c>
+      <c r="C733">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="734" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B734" s="2">
+        <v>785</v>
+      </c>
+      <c r="C734">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="735" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B735" s="2">
+        <v>786</v>
+      </c>
+      <c r="C735">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="736" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B736" s="2">
+        <v>787</v>
+      </c>
+      <c r="C736">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="737" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B737" s="2">
+        <v>788</v>
+      </c>
+      <c r="C737">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="738" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B738" s="2">
+        <v>789</v>
+      </c>
+      <c r="C738">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="739" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B739" s="2">
+        <v>790</v>
+      </c>
+      <c r="C739">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="740" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B740" s="2">
+        <v>791</v>
+      </c>
+      <c r="C740">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="741" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B741" s="2">
+        <v>792</v>
+      </c>
+      <c r="C741">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="742" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B742" s="2">
+        <v>793</v>
+      </c>
+      <c r="C742">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="743" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B743" s="2">
+        <v>794</v>
+      </c>
+      <c r="C743">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="744" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B744" s="2">
+        <v>795</v>
+      </c>
+      <c r="C744">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="745" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B745" s="2">
+        <v>796</v>
+      </c>
+      <c r="C745">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="746" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B746" s="2">
+        <v>797</v>
+      </c>
+      <c r="C746">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="747" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B747" s="2">
+        <v>798</v>
+      </c>
+      <c r="C747">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="748" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B748" s="2">
+        <v>799</v>
+      </c>
+      <c r="C748">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="749" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B749" s="2">
+        <v>800</v>
+      </c>
+      <c r="C749">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="750" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B750" s="2">
+        <v>801</v>
+      </c>
+      <c r="C750">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="751" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B751" s="2">
+        <v>802</v>
+      </c>
+      <c r="C751">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="752" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B752" s="2">
+        <v>803</v>
+      </c>
+      <c r="C752">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="753" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B753" s="2">
+        <v>804</v>
+      </c>
+      <c r="C753">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="754" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B754" s="2">
+        <v>805</v>
+      </c>
+      <c r="C754">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="755" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B755" s="2">
+        <v>806</v>
+      </c>
+      <c r="C755">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="756" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B756" s="2">
+        <v>807</v>
+      </c>
+      <c r="C756">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="757" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B757" s="2">
+        <v>808</v>
+      </c>
+      <c r="C757">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="758" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B758" s="2">
+        <v>809</v>
+      </c>
+      <c r="C758">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="759" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B759" s="2">
+        <v>810</v>
+      </c>
+      <c r="C759">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="760" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B760" s="2">
+        <v>811</v>
+      </c>
+      <c r="C760">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="761" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B761" s="2">
+        <v>812</v>
+      </c>
+      <c r="C761">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="762" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B762" s="2">
+        <v>813</v>
+      </c>
+      <c r="C762">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="763" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B763" s="2">
+        <v>816</v>
+      </c>
+      <c r="C763">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="764" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B764" s="2">
+        <v>817</v>
+      </c>
+      <c r="C764">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="765" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B765" s="2">
+        <v>818</v>
+      </c>
+      <c r="C765">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="766" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B766" s="2">
+        <v>819</v>
+      </c>
+      <c r="C766">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="767" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B767" s="2">
+        <v>827</v>
+      </c>
+      <c r="C767">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="768" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B768" s="2">
+        <v>828</v>
+      </c>
+      <c r="C768">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="769" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B769" s="2">
+        <v>829</v>
+      </c>
+      <c r="C769">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="770" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B770" s="2">
+        <v>830</v>
+      </c>
+      <c r="C770">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="771" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B771" s="2">
+        <v>852</v>
+      </c>
+      <c r="C771">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="772" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B772" s="2">
+        <v>853</v>
+      </c>
+      <c r="C772">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="773" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B773" s="2">
+        <v>854</v>
+      </c>
+      <c r="C773">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="774" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B774" s="2">
+        <v>855</v>
+      </c>
+      <c r="C774">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="775" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B775" s="2">
+        <v>856</v>
+      </c>
+      <c r="C775">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="776" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B776" s="2">
+        <v>857</v>
+      </c>
+      <c r="C776">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="777" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B777" s="2">
+        <v>858</v>
+      </c>
+      <c r="C777">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="778" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B778" s="2">
+        <v>859</v>
+      </c>
+      <c r="C778">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="779" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B779" s="2">
+        <v>860</v>
+      </c>
+      <c r="C779">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="780" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B780" s="2">
+        <v>861</v>
+      </c>
+      <c r="C780">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="781" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B781" s="2">
+        <v>862</v>
+      </c>
+      <c r="C781">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="782" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B782" s="2">
+        <v>863</v>
+      </c>
+      <c r="C782">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="783" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B783" s="2">
+        <v>864</v>
+      </c>
+      <c r="C783">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="784" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B784" s="2">
+        <v>865</v>
+      </c>
+      <c r="C784">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="785" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B785" s="2">
+        <v>866</v>
+      </c>
+      <c r="C785">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="786" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B786" s="2">
+        <v>890</v>
+      </c>
+      <c r="C786">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="787" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B787" s="2">
+        <v>891</v>
+      </c>
+      <c r="C787">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="788" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B788" s="2">
+        <v>897</v>
+      </c>
+      <c r="C788">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="789" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B789" s="2">
+        <v>898</v>
+      </c>
+      <c r="C789">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="790" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B790" s="2">
+        <v>899</v>
+      </c>
+      <c r="C790">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="791" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B791" s="2">
+        <v>903</v>
+      </c>
+      <c r="C791">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="792" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B792" s="2">
+        <v>905</v>
+      </c>
+      <c r="C792">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="793" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B793" s="2">
+        <v>906</v>
+      </c>
+      <c r="C793">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="794" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B794" s="2">
+        <v>907</v>
+      </c>
+      <c r="C794">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="795" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B795" s="2">
+        <v>908</v>
+      </c>
+      <c r="C795">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="796" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B796" s="2">
+        <v>909</v>
+      </c>
+      <c r="C796">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="797" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B797" s="2">
+        <v>910</v>
+      </c>
+      <c r="C797">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="798" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B798" s="2">
+        <v>911</v>
+      </c>
+      <c r="C798">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="799" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B799" s="2">
+        <v>912</v>
+      </c>
+      <c r="C799">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="800" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B800" s="2">
+        <v>913</v>
+      </c>
+      <c r="C800">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="801" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B801" s="2">
+        <v>914</v>
+      </c>
+      <c r="C801">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="802" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B802" s="2">
+        <v>915</v>
+      </c>
+      <c r="C802">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="803" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B803" s="2">
+        <v>916</v>
+      </c>
+      <c r="C803">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="804" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B804" s="2">
+        <v>917</v>
+      </c>
+      <c r="C804">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="805" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B805" s="2">
+        <v>918</v>
+      </c>
+      <c r="C805">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="806" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B806" s="2">
+        <v>919</v>
+      </c>
+      <c r="C806">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="807" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B807" s="2">
+        <v>920</v>
+      </c>
+      <c r="C807">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="808" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B808" s="2">
+        <v>921</v>
+      </c>
+      <c r="C808">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="809" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B809" s="2">
+        <v>922</v>
+      </c>
+      <c r="C809">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="810" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B810" s="2">
+        <v>923</v>
+      </c>
+      <c r="C810">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="811" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B811" s="2">
+        <v>924</v>
+      </c>
+      <c r="C811">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="812" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B812" s="2">
+        <v>925</v>
+      </c>
+      <c r="C812">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="813" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B813" s="2">
+        <v>926</v>
+      </c>
+      <c r="C813">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="814" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B814" s="2">
+        <v>927</v>
+      </c>
+      <c r="C814">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="815" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B815" s="2">
+        <v>928</v>
+      </c>
+      <c r="C815">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="816" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B816" s="2">
+        <v>929</v>
+      </c>
+      <c r="C816">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="817" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B817" s="2">
+        <v>931</v>
+      </c>
+      <c r="C817">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="818" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B818" s="2">
+        <v>932</v>
+      </c>
+      <c r="C818">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="819" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B819" s="2">
+        <v>933</v>
+      </c>
+      <c r="C819">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="820" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B820" s="2">
+        <v>934</v>
+      </c>
+      <c r="C820">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="821" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B821" s="2">
+        <v>940</v>
+      </c>
+      <c r="C821">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="822" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B822" s="2">
+        <v>941</v>
+      </c>
+      <c r="C822">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="823" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B823" s="2">
+        <v>942</v>
+      </c>
+      <c r="C823">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="824" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B824" s="2">
+        <v>943</v>
+      </c>
+      <c r="C824">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="825" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B825" s="2">
+        <v>944</v>
+      </c>
+      <c r="C825">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="826" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B826" s="2">
+        <v>945</v>
+      </c>
+      <c r="C826">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="827" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B827" s="2">
+        <v>946</v>
+      </c>
+      <c r="C827">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="828" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B828" s="2">
+        <v>947</v>
+      </c>
+      <c r="C828">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="829" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B829" s="2">
+        <v>948</v>
+      </c>
+      <c r="C829">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="830" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B830" s="2">
+        <v>949</v>
+      </c>
+      <c r="C830">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="831" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B831" s="2">
+        <v>950</v>
+      </c>
+      <c r="C831">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="832" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B832" s="2">
+        <v>951</v>
+      </c>
+      <c r="C832">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="833" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B833" s="2">
+        <v>952</v>
+      </c>
+      <c r="C833">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="834" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B834" s="2">
+        <v>953</v>
+      </c>
+      <c r="C834">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="835" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B835" s="2">
+        <v>954</v>
+      </c>
+      <c r="C835">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="836" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B836" s="2">
+        <v>955</v>
+      </c>
+      <c r="C836">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="837" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B837" s="2">
+        <v>956</v>
+      </c>
+      <c r="C837">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="838" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B838" s="2">
+        <v>957</v>
+      </c>
+      <c r="C838">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="839" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B839" s="2">
+        <v>958</v>
+      </c>
+      <c r="C839">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="840" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B840" s="2">
+        <v>959</v>
+      </c>
+      <c r="C840">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="841" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B841" s="2">
+        <v>960</v>
+      </c>
+      <c r="C841">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="842" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B842" s="2">
+        <v>961</v>
+      </c>
+      <c r="C842">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="843" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B843" s="2">
+        <v>962</v>
+      </c>
+      <c r="C843">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="844" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B844" s="2">
+        <v>963</v>
+      </c>
+      <c r="C844">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="845" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B845" s="2">
+        <v>968</v>
+      </c>
+      <c r="C845">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="846" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B846" s="2">
+        <v>969</v>
+      </c>
+      <c r="C846">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="847" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B847" s="2">
+        <v>970</v>
+      </c>
+      <c r="C847">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="848" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B848" s="2">
+        <v>971</v>
+      </c>
+      <c r="C848">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="849" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B849" s="2">
+        <v>974</v>
+      </c>
+      <c r="C849">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="850" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B850" s="2">
+        <v>975</v>
+      </c>
+      <c r="C850">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="851" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B851" s="2">
+        <v>976</v>
+      </c>
+      <c r="C851">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="852" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B852" s="2">
+        <v>977</v>
+      </c>
+      <c r="C852">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="853" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B853" s="2">
+        <v>978</v>
+      </c>
+      <c r="C853">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="854" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B854" s="2">
+        <v>979</v>
+      </c>
+      <c r="C854">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="855" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B855" s="2">
+        <v>980</v>
+      </c>
+      <c r="C855">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="856" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B856" s="2">
+        <v>981</v>
+      </c>
+      <c r="C856">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="857" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B857" s="2">
+        <v>982</v>
+      </c>
+      <c r="C857">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="858" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B858" s="2">
+        <v>983</v>
+      </c>
+      <c r="C858">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="859" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B859" s="2">
+        <v>984</v>
+      </c>
+      <c r="C859">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="860" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B860" s="2">
+        <v>985</v>
+      </c>
+      <c r="C860">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="861" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B861" s="2">
+        <v>986</v>
+      </c>
+      <c r="C861">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="862" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B862" s="2">
+        <v>987</v>
+      </c>
+      <c r="C862">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="863" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B863" s="2">
+        <v>988</v>
+      </c>
+      <c r="C863">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="864" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B864" s="2">
+        <v>989</v>
+      </c>
+      <c r="C864">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="865" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B865" s="2">
+        <v>990</v>
+      </c>
+      <c r="C865">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="866" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B866" s="2">
+        <v>991</v>
+      </c>
+      <c r="C866">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="867" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B867" s="2">
+        <v>992</v>
+      </c>
+      <c r="C867">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="868" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B868" s="2">
+        <v>993</v>
+      </c>
+      <c r="C868">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="869" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B869" s="2">
+        <v>994</v>
+      </c>
+      <c r="C869">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="870" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B870" s="2">
+        <v>995</v>
+      </c>
+      <c r="C870">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="871" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B871" s="2">
+        <v>996</v>
+      </c>
+      <c r="C871">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="872" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B872" s="2">
+        <v>997</v>
+      </c>
+      <c r="C872">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="873" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B873" s="2">
+        <v>998</v>
+      </c>
+      <c r="C873">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="874" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B874" s="2">
+        <v>999</v>
+      </c>
+      <c r="C874">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="875" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B875" s="2">
+        <v>1000</v>
+      </c>
+      <c r="C875">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="876" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B876" s="2">
+        <v>1001</v>
+      </c>
+      <c r="C876">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="877" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B877" s="2">
+        <v>1002</v>
+      </c>
+      <c r="C877">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="878" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B878" s="2">
+        <v>1003</v>
+      </c>
+      <c r="C878">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="879" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B879" s="2">
+        <v>1004</v>
+      </c>
+      <c r="C879">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="880" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B880" s="2">
+        <v>1005</v>
+      </c>
+      <c r="C880">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="881" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B881" s="2">
+        <v>1006</v>
+      </c>
+      <c r="C881">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="882" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B882" s="2">
+        <v>1007</v>
+      </c>
+      <c r="C882">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="883" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B883" s="2">
+        <v>1010</v>
+      </c>
+      <c r="C883">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="884" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B884" s="2">
+        <v>1011</v>
+      </c>
+      <c r="C884">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="885" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B885" s="2">
+        <v>1012</v>
+      </c>
+      <c r="C885">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="886" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B886" s="2">
+        <v>1013</v>
+      </c>
+      <c r="C886">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="887" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B887" s="2">
+        <v>1014</v>
+      </c>
+      <c r="C887">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="888" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B888" s="2">
+        <v>1015</v>
+      </c>
+      <c r="C888">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="889" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B889" s="2">
+        <v>1016</v>
+      </c>
+      <c r="C889">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="890" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B890" s="2">
+        <v>1017</v>
+      </c>
+      <c r="C890">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="891" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B891" s="2">
+        <v>1019</v>
+      </c>
+      <c r="C891">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="892" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B892" s="2">
+        <v>1020</v>
+      </c>
+      <c r="C892">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="893" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B893" s="2">
+        <v>1021</v>
+      </c>
+      <c r="C893">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="894" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B894" s="2">
+        <v>1022</v>
+      </c>
+      <c r="C894">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="895" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B895" s="2">
+        <v>1023</v>
+      </c>
+      <c r="C895">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="896" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B896" s="2">
+        <v>1024</v>
+      </c>
+      <c r="C896">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="897" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B897" s="2">
+        <v>1025</v>
+      </c>
+      <c r="C897">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="898" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B898" s="2">
+        <v>1026</v>
+      </c>
+      <c r="C898">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="899" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B899" s="2">
+        <v>1027</v>
+      </c>
+      <c r="C899">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="900" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B900" s="2">
+        <v>1028</v>
+      </c>
+      <c r="C900">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="901" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B901" s="2">
+        <v>1029</v>
+      </c>
+      <c r="C901">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="902" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B902" s="2">
+        <v>1030</v>
+      </c>
+      <c r="C902">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="903" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B903" s="2">
+        <v>1031</v>
+      </c>
+      <c r="C903">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="904" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B904" s="2">
+        <v>1032</v>
+      </c>
+      <c r="C904">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="905" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B905" s="2">
+        <v>1033</v>
+      </c>
+      <c r="C905">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="906" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B906" s="2">
+        <v>1034</v>
+      </c>
+      <c r="C906">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="907" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B907" s="2">
+        <v>1035</v>
+      </c>
+      <c r="C907">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="908" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B908" s="2">
+        <v>1036</v>
+      </c>
+      <c r="C908">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="909" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B909" s="2">
+        <v>1037</v>
+      </c>
+      <c r="C909">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="910" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B910" s="2">
+        <v>1038</v>
+      </c>
+      <c r="C910">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="911" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B911" s="2">
+        <v>1039</v>
+      </c>
+      <c r="C911">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="912" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B912" s="2">
+        <v>1040</v>
+      </c>
+      <c r="C912">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="913" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B913" s="2">
+        <v>1041</v>
+      </c>
+      <c r="C913">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="914" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B914" s="2">
+        <v>1042</v>
+      </c>
+      <c r="C914">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="915" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B915" s="2">
+        <v>1043</v>
+      </c>
+      <c r="C915">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="916" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B916" s="2">
+        <v>1044</v>
+      </c>
+      <c r="C916">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="917" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B917" s="2">
+        <v>1045</v>
+      </c>
+      <c r="C917">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="918" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B918" s="2">
+        <v>1046</v>
+      </c>
+      <c r="C918">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="919" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B919" s="2">
+        <v>1047</v>
+      </c>
+      <c r="C919">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="920" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B920" s="2">
+        <v>1052</v>
+      </c>
+      <c r="C920">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="921" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B921" s="2">
+        <v>1053</v>
+      </c>
+      <c r="C921">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="922" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B922" s="2">
+        <v>1054</v>
+      </c>
+      <c r="C922">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="923" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B923" s="2">
+        <v>1055</v>
+      </c>
+      <c r="C923">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="924" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B924" s="2">
+        <v>1056</v>
+      </c>
+      <c r="C924">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="925" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B925" s="2">
+        <v>1057</v>
+      </c>
+      <c r="C925">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="926" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B926" s="2">
+        <v>1058</v>
+      </c>
+      <c r="C926">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="927" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B927" s="2">
+        <v>1059</v>
+      </c>
+      <c r="C927">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="928" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B928" s="2">
+        <v>1060</v>
+      </c>
+      <c r="C928">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="929" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B929" s="2">
+        <v>1061</v>
+      </c>
+      <c r="C929">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="930" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B930" s="2">
+        <v>1062</v>
+      </c>
+      <c r="C930">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="931" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B931" s="2">
+        <v>1063</v>
+      </c>
+      <c r="C931">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="932" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B932" s="2">
+        <v>1064</v>
+      </c>
+      <c r="C932">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="933" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B933" s="2">
+        <v>1065</v>
+      </c>
+      <c r="C933">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="934" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B934" s="2">
+        <v>1066</v>
+      </c>
+      <c r="C934">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="935" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B935" s="2">
+        <v>1067</v>
+      </c>
+      <c r="C935">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="936" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B936" s="2">
+        <v>1068</v>
+      </c>
+      <c r="C936">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="937" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B937" s="2">
+        <v>1069</v>
+      </c>
+      <c r="C937">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="938" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B938" s="2">
+        <v>1070</v>
+      </c>
+      <c r="C938">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="939" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B939" s="2">
+        <v>1071</v>
+      </c>
+      <c r="C939">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="940" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B940" s="2">
+        <v>1072</v>
+      </c>
+      <c r="C940">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="941" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B941" s="2">
+        <v>1075</v>
+      </c>
+      <c r="C941">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="942" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B942" s="2">
+        <v>1076</v>
+      </c>
+      <c r="C942">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="943" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B943" s="2">
+        <v>1077</v>
+      </c>
+      <c r="C943">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="944" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B944" s="2">
+        <v>1078</v>
+      </c>
+      <c r="C944">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="945" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B945" s="2">
+        <v>1079</v>
+      </c>
+      <c r="C945">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="946" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B946" s="2">
+        <v>1080</v>
+      </c>
+      <c r="C946">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="947" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B947" s="2">
+        <v>1081</v>
+      </c>
+      <c r="C947">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="948" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B948" s="2">
+        <v>1082</v>
+      </c>
+      <c r="C948">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="949" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B949" s="2">
+        <v>1083</v>
+      </c>
+      <c r="C949">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="950" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B950" s="2">
+        <v>1084</v>
+      </c>
+      <c r="C950">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="951" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B951" s="2">
+        <v>1085</v>
+      </c>
+      <c r="C951">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="952" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B952" s="2">
+        <v>1086</v>
+      </c>
+      <c r="C952">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="953" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B953" s="2">
+        <v>1087</v>
+      </c>
+      <c r="C953">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="954" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B954" s="2">
+        <v>1088</v>
+      </c>
+      <c r="C954">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="955" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B955" s="2">
+        <v>1089</v>
+      </c>
+      <c r="C955">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="956" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B956" s="2">
+        <v>1090</v>
+      </c>
+      <c r="C956">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="957" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B957" s="2">
+        <v>1091</v>
+      </c>
+      <c r="C957">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="958" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B958" s="2">
+        <v>1092</v>
+      </c>
+      <c r="C958">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="959" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B959" s="2">
+        <v>1093</v>
+      </c>
+      <c r="C959">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="960" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B960" s="2">
+        <v>1094</v>
+      </c>
+      <c r="C960">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="961" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B961" s="2">
+        <v>1095</v>
+      </c>
+      <c r="C961">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="962" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B962" s="2">
+        <v>1096</v>
+      </c>
+      <c r="C962">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="963" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B963" s="2">
+        <v>1097</v>
+      </c>
+      <c r="C963">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="964" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B964" s="2">
+        <v>1100</v>
+      </c>
+      <c r="C964">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="965" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B965" s="2">
+        <v>1101</v>
+      </c>
+      <c r="C965">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="966" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B966" s="2">
+        <v>1102</v>
+      </c>
+      <c r="C966">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="967" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B967" s="2">
+        <v>1103</v>
+      </c>
+      <c r="C967">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="968" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B968" s="2">
+        <v>1104</v>
+      </c>
+      <c r="C968">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="969" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B969" s="2">
+        <v>1105</v>
+      </c>
+      <c r="C969">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="970" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B970" s="2">
+        <v>1106</v>
+      </c>
+      <c r="C970">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="971" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B971" s="2">
+        <v>1107</v>
+      </c>
+      <c r="C971">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="972" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B972" s="2">
+        <v>1108</v>
+      </c>
+      <c r="C972">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="973" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B973" s="2">
+        <v>1109</v>
+      </c>
+      <c r="C973">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="974" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B974" s="2">
+        <v>1110</v>
+      </c>
+      <c r="C974">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="975" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B975" s="2">
+        <v>1111</v>
+      </c>
+      <c r="C975">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="976" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B976" s="2">
+        <v>1112</v>
+      </c>
+      <c r="C976">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="977" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B977" s="2">
+        <v>1113</v>
+      </c>
+      <c r="C977">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="978" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B978" s="2">
+        <v>1114</v>
+      </c>
+      <c r="C978">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="979" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B979" s="2">
+        <v>1115</v>
+      </c>
+      <c r="C979">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="980" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B980" s="2">
+        <v>1116</v>
+      </c>
+      <c r="C980">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="981" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B981" s="2">
+        <v>1117</v>
+      </c>
+      <c r="C981">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="982" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B982" s="2">
+        <v>1125</v>
+      </c>
+      <c r="C982">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="983" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B983" s="2">
+        <v>1126</v>
+      </c>
+      <c r="C983">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="984" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B984" s="2">
+        <v>1127</v>
+      </c>
+      <c r="C984">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="985" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B985" s="2">
+        <v>1128</v>
+      </c>
+      <c r="C985">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="986" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B986" s="2">
+        <v>1129</v>
+      </c>
+      <c r="C986">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="987" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B987" s="2">
+        <v>1130</v>
+      </c>
+      <c r="C987">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="988" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B988" s="2">
+        <v>1131</v>
+      </c>
+      <c r="C988">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="989" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B989" s="2">
+        <v>1132</v>
+      </c>
+      <c r="C989">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="990" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B990" s="2">
+        <v>1133</v>
+      </c>
+      <c r="C990">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="991" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B991" s="2">
+        <v>1134</v>
+      </c>
+      <c r="C991">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="992" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B992" s="2">
+        <v>1135</v>
+      </c>
+      <c r="C992">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="993" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B993" s="2">
+        <v>1136</v>
+      </c>
+      <c r="C993">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="994" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B994" s="2">
+        <v>1137</v>
+      </c>
+      <c r="C994">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="995" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B995" s="2">
+        <v>1138</v>
+      </c>
+      <c r="C995">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="996" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B996" s="2">
+        <v>1139</v>
+      </c>
+      <c r="C996">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="997" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B997" s="2">
+        <v>1140</v>
+      </c>
+      <c r="C997">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="998" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B998" s="2">
+        <v>1141</v>
+      </c>
+      <c r="C998">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="999" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B999" s="2">
+        <v>1142</v>
+      </c>
+      <c r="C999">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1000" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1000" s="2">
+        <v>1143</v>
+      </c>
+      <c r="C1000">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1001" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1001" s="2">
+        <v>1146</v>
+      </c>
+      <c r="C1001">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1002" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1002" s="2">
+        <v>1147</v>
+      </c>
+      <c r="C1002">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1003" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1003" s="2">
+        <v>1148</v>
+      </c>
+      <c r="C1003">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1004" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1004" s="2">
+        <v>1149</v>
+      </c>
+      <c r="C1004">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1005" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1005" s="2">
+        <v>1150</v>
+      </c>
+      <c r="C1005">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1006" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1006" s="2">
+        <v>1151</v>
+      </c>
+      <c r="C1006">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1007" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1007" s="2">
+        <v>1152</v>
+      </c>
+      <c r="C1007">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1008" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1008" s="2">
+        <v>1153</v>
+      </c>
+      <c r="C1008">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1009" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1009" s="2">
+        <v>1154</v>
+      </c>
+      <c r="C1009">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1010" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1010" s="2">
+        <v>1155</v>
+      </c>
+      <c r="C1010">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1011" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1011" s="2">
+        <v>1156</v>
+      </c>
+      <c r="C1011">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1012" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1012" s="2">
+        <v>1157</v>
+      </c>
+      <c r="C1012">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1013" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1013" s="2">
+        <v>1158</v>
+      </c>
+      <c r="C1013">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1014" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1014" s="2">
+        <v>1159</v>
+      </c>
+      <c r="C1014">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1015" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1015" s="2">
+        <v>1160</v>
+      </c>
+      <c r="C1015">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1016" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1016" s="2">
+        <v>1161</v>
+      </c>
+      <c r="C1016">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1017" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1017" s="2">
+        <v>1162</v>
+      </c>
+      <c r="C1017">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1018" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1018" s="2">
+        <v>1163</v>
+      </c>
+      <c r="C1018">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1019" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1019" s="2">
+        <v>1164</v>
+      </c>
+      <c r="C1019">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1020" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1020" s="2">
+        <v>1165</v>
+      </c>
+      <c r="C1020">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1021" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1021" s="2">
+        <v>1166</v>
+      </c>
+      <c r="C1021">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1022" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1022" s="2">
+        <v>1167</v>
+      </c>
+      <c r="C1022">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1023" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1023" s="2">
+        <v>1168</v>
+      </c>
+      <c r="C1023">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1024" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1024" s="2">
+        <v>1169</v>
+      </c>
+      <c r="C1024">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1025" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1025" s="2">
+        <v>1180</v>
+      </c>
+      <c r="C1025">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1026" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1026" s="2">
+        <v>1208</v>
+      </c>
+      <c r="C1026">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1027" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1027" s="2">
+        <v>1216</v>
+      </c>
+      <c r="C1027">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1028" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1028" s="2">
+        <v>1217</v>
+      </c>
+      <c r="C1028">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1029" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1029" s="2">
+        <v>1218</v>
+      </c>
+      <c r="C1029">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1030" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1030" s="2">
+        <v>1219</v>
+      </c>
+      <c r="C1030">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1031" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1031" s="2">
+        <v>1220</v>
+      </c>
+      <c r="C1031">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1032" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1032" s="2">
+        <v>1221</v>
+      </c>
+      <c r="C1032">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1033" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1033" s="2">
+        <v>1222</v>
+      </c>
+      <c r="C1033">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1034" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1034" s="2">
+        <v>1223</v>
+      </c>
+      <c r="C1034">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1035" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1035" s="2">
+        <v>1224</v>
+      </c>
+      <c r="C1035">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1036" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1036" s="2">
+        <v>1225</v>
+      </c>
+      <c r="C1036">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1037" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1037" s="2">
+        <v>1226</v>
+      </c>
+      <c r="C1037">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1038" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1038" s="2">
+        <v>1227</v>
+      </c>
+      <c r="C1038">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1039" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1039" s="2">
+        <v>1228</v>
+      </c>
+      <c r="C1039">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1040" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1040" s="2">
+        <v>1229</v>
+      </c>
+      <c r="C1040">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1041" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1041" s="2">
+        <v>1230</v>
+      </c>
+      <c r="C1041">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1042" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1042" s="2">
+        <v>1231</v>
+      </c>
+      <c r="C1042">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1043" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1043" s="2">
+        <v>1232</v>
+      </c>
+      <c r="C1043">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1044" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1044" s="2">
+        <v>1233</v>
+      </c>
+      <c r="C1044">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1045" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1045" s="2">
+        <v>1234</v>
+      </c>
+      <c r="C1045">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1046" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1046" s="2">
+        <v>1237</v>
+      </c>
+      <c r="C1046">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1047" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1047" s="2">
+        <v>1238</v>
+      </c>
+      <c r="C1047">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1048" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1048" s="2">
+        <v>1239</v>
+      </c>
+      <c r="C1048">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1049" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1049" s="2">
+        <v>1240</v>
+      </c>
+      <c r="C1049">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1050" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1050" s="2">
+        <v>1241</v>
+      </c>
+      <c r="C1050">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1051" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1051" s="2">
+        <v>1242</v>
+      </c>
+      <c r="C1051">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1052" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1052" s="2">
+        <v>1243</v>
+      </c>
+      <c r="C1052">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1053" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1053" s="2">
+        <v>1244</v>
+      </c>
+      <c r="C1053">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1054" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1054" s="2">
+        <v>1245</v>
+      </c>
+      <c r="C1054">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1055" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1055" s="2">
+        <v>1246</v>
+      </c>
+      <c r="C1055">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1056" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1056" s="2">
+        <v>1247</v>
+      </c>
+      <c r="C1056">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1057" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1057" s="2">
+        <v>1248</v>
+      </c>
+      <c r="C1057">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1058" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1058" s="2">
+        <v>1249</v>
+      </c>
+      <c r="C1058">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1059" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1059" s="2">
+        <v>1250</v>
+      </c>
+      <c r="C1059">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1060" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1060" s="2">
+        <v>1251</v>
+      </c>
+      <c r="C1060">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1061" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1061" s="2">
+        <v>1252</v>
+      </c>
+      <c r="C1061">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1062" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1062" s="2">
+        <v>1253</v>
+      </c>
+      <c r="C1062">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1063" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1063" s="2">
+        <v>1254</v>
+      </c>
+      <c r="C1063">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1064" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1064" s="2">
+        <v>1255</v>
+      </c>
+      <c r="C1064">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1065" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1065" s="2">
+        <v>1256</v>
+      </c>
+      <c r="C1065">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1066" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1066" s="2">
+        <v>1257</v>
+      </c>
+      <c r="C1066">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1067" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1067" s="2">
+        <v>1258</v>
+      </c>
+      <c r="C1067">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1068" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1068" s="2">
+        <v>1259</v>
+      </c>
+      <c r="C1068">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1069" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1069" s="2">
+        <v>1260</v>
+      </c>
+      <c r="C1069">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1070" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1070" s="2">
+        <v>1261</v>
+      </c>
+      <c r="C1070">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1071" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1071" s="2">
+        <v>1262</v>
+      </c>
+      <c r="C1071">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1072" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1072" s="2">
+        <v>1263</v>
+      </c>
+      <c r="C1072">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1073" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1073" s="2">
+        <v>1265</v>
+      </c>
+      <c r="C1073">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1074" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1074" s="2">
+        <v>1266</v>
+      </c>
+      <c r="C1074">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1075" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1075" s="2">
+        <v>1267</v>
+      </c>
+      <c r="C1075">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1076" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1076" s="2">
+        <v>1268</v>
+      </c>
+      <c r="C1076">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1077" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1077" s="2">
+        <v>1269</v>
+      </c>
+      <c r="C1077">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1078" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1078" s="2">
+        <v>1270</v>
+      </c>
+      <c r="C1078">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1079" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1079" s="2">
+        <v>1271</v>
+      </c>
+      <c r="C1079">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1080" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1080" s="2">
+        <v>1272</v>
+      </c>
+      <c r="C1080">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1081" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1081" s="2">
+        <v>1273</v>
+      </c>
+      <c r="C1081">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1082" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1082" s="2">
+        <v>1275</v>
+      </c>
+      <c r="C1082">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1083" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1083" s="2">
+        <v>1276</v>
+      </c>
+      <c r="C1083">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1084" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1084" s="2">
+        <v>1277</v>
+      </c>
+      <c r="C1084">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1085" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1085" s="2">
+        <v>1278</v>
+      </c>
+      <c r="C1085">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1086" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1086" s="2">
+        <v>1279</v>
+      </c>
+      <c r="C1086">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1087" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1087" s="2">
+        <v>1280</v>
+      </c>
+      <c r="C1087">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1088" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1088" s="2">
+        <v>1281</v>
+      </c>
+      <c r="C1088">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1089" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1089" s="2">
+        <v>1282</v>
+      </c>
+      <c r="C1089">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1090" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1090" s="2">
+        <v>1283</v>
+      </c>
+      <c r="C1090">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1091" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1091" s="2">
+        <v>1284</v>
+      </c>
+      <c r="C1091">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1092" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1092" s="2">
+        <v>1285</v>
+      </c>
+      <c r="C1092">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1093" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1093" s="2">
+        <v>1286</v>
+      </c>
+      <c r="C1093">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1094" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1094" s="2">
+        <v>1287</v>
+      </c>
+      <c r="C1094">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1095" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1095" s="2">
+        <v>1288</v>
+      </c>
+      <c r="C1095">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1096" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1096" s="2">
+        <v>1289</v>
+      </c>
+      <c r="C1096">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1097" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1097" s="2">
+        <v>1290</v>
+      </c>
+      <c r="C1097">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1098" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1098" s="2">
+        <v>1291</v>
+      </c>
+      <c r="C1098">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1099" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1099" s="2">
+        <v>1292</v>
+      </c>
+      <c r="C1099">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1100" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1100" s="2">
+        <v>1295</v>
+      </c>
+      <c r="C1100">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>